--- a/GPIO.xlsx
+++ b/GPIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhui\AppData\Roaming\32\workspace\f407igt6_Car\f407IGT6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8ED836B-0246-4051-844E-0C57239382BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217F61F-6B1D-418E-B9F6-FCFDE8DEE348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GPIO.xlsx
+++ b/GPIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhui\AppData\Roaming\32\workspace\f407igt6_Car\f407IGT6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217F61F-6B1D-418E-B9F6-FCFDE8DEE348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B9B75D-02B2-456D-AE32-855BC0E90C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>芯片型号:</t>
   </si>
@@ -226,19 +226,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I2C1-SDA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C1-SCL </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PG15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>I2C地址选择引脚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BH1750_I2C1-SDA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务板光敏电阻传感器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BH1750_I2C1-SCL </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                         PC6  (波特率115200)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">语音串口-UART6-Tx </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音串口-UART6-Rx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                     PA9(波特率9600)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF读卡器_UART1-Tx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF读卡器_UART1-Rx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="F1:K41"/>
+  <dimension ref="F1:K43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="4.5" customWidth="1"/>
@@ -663,6 +707,9 @@
       </c>
     </row>
     <row r="11" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H11" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="J11" s="2" t="s">
         <v>19</v>
       </c>
@@ -671,6 +718,9 @@
       </c>
     </row>
     <row r="12" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H12" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="J12" s="2" t="s">
         <v>20</v>
       </c>
@@ -679,6 +729,9 @@
       </c>
     </row>
     <row r="13" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H13" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="J13" s="2" t="s">
         <v>21</v>
       </c>
@@ -687,6 +740,9 @@
       </c>
     </row>
     <row r="14" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H14" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="J14" s="2" t="s">
         <v>22</v>
       </c>
@@ -695,6 +751,9 @@
       </c>
     </row>
     <row r="16" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="J16" s="2" t="s">
         <v>27</v>
       </c>
@@ -703,6 +762,9 @@
       </c>
     </row>
     <row r="17" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H17" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="J17" s="2" t="s">
         <v>28</v>
       </c>
@@ -711,6 +773,9 @@
       </c>
     </row>
     <row r="18" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H18" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="J18" s="2" t="s">
         <v>29</v>
       </c>
@@ -719,6 +784,9 @@
       </c>
     </row>
     <row r="19" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H19" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="J19" s="2" t="s">
         <v>30</v>
       </c>
@@ -802,7 +870,7 @@
     </row>
     <row r="33" spans="8:11" x14ac:dyDescent="0.2">
       <c r="J33" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>51</v>
@@ -810,7 +878,7 @@
     </row>
     <row r="34" spans="8:11" x14ac:dyDescent="0.2">
       <c r="J34" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>50</v>
@@ -821,29 +889,63 @@
         <v>35</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="8:11" x14ac:dyDescent="0.2">
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="K37" s="2"/>
+      <c r="J37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="38" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="K38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="39" spans="8:11" x14ac:dyDescent="0.2">
       <c r="K39" s="2"/>
     </row>
     <row r="40" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="K40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="41" spans="8:11" x14ac:dyDescent="0.2">
       <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="J42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="J43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
